--- a/Restoration Mountaine Forest - Seed Dispersal (with_NTFP).xlsx
+++ b/Restoration Mountaine Forest - Seed Dispersal (with_NTFP).xlsx
@@ -3683,7 +3683,7 @@
         <v>coffea arabica</v>
       </c>
       <c r="FL5">
-        <v>80</v>
+        <v>4.64</v>
       </c>
       <c r="FM5">
         <v>1</v>
